--- a/docs/Donna_Canonico.xlsx
+++ b/docs/Donna_Canonico.xlsx
@@ -18,9 +18,10 @@
     <sheet name="Transacciones" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Categorias" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Metas" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Tarjetas y Deuda" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Dashboard" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Comparativo" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Compras_Detalle" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Tarjetas y Deuda" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Dashboard" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Comparativo" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -985,29 +986,29 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.15" customHeight="1" s="36">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>🏷️ CATEGORÍAS — única fuente de presupuestos.</t>
         </is>
       </c>
     </row>
     <row r="2" ht="23.85" customHeight="1" s="36">
-      <c r="A2" s="52" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="B2" s="52" t="inlineStr">
+      <c r="B2" s="53" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C2" s="52" t="inlineStr">
+      <c r="C2" s="53" t="inlineStr">
         <is>
           <t>Presupuesto Mensual</t>
         </is>
       </c>
-      <c r="D2" s="52" t="inlineStr">
+      <c r="D2" s="53" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -1436,6 +1437,91 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="36" min="1" max="1"/>
+    <col width="18" customWidth="1" style="36" min="2" max="2"/>
+    <col width="22" customWidth="1" style="36" min="3" max="3"/>
+    <col width="9" customWidth="1" style="36" min="4" max="4"/>
+    <col width="10" customWidth="1" style="36" min="5" max="5"/>
+    <col width="14" customWidth="1" style="36" min="6" max="6"/>
+    <col width="12" customWidth="1" style="36" min="7" max="7"/>
+    <col width="11" customWidth="1" style="36" min="8" max="8"/>
+    <col width="18" customWidth="1" style="36" min="9" max="9"/>
+    <col width="9" customWidth="1" style="36" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="59" t="inlineStr">
+        <is>
+          <t>🧾 COMPRAS_DETALLE — el detalle ítem-a-ítem de una compra (v3). Una transacción de Transacciones puede tener varias líneas acá (ID_Tx = ID_Único del padre).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="53" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B2" s="53" t="inlineStr">
+        <is>
+          <t>Comercio</t>
+        </is>
+      </c>
+      <c r="C2" s="53" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D2" s="53" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E2" s="53" t="inlineStr">
+        <is>
+          <t>Precio</t>
+        </is>
+      </c>
+      <c r="F2" s="53" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="G2" s="53" t="inlineStr">
+        <is>
+          <t>Intención</t>
+        </is>
+      </c>
+      <c r="H2" s="53" t="inlineStr">
+        <is>
+          <t>Predecible</t>
+        </is>
+      </c>
+      <c r="I2" s="53" t="inlineStr">
+        <is>
+          <t>ID_Tx</t>
+        </is>
+      </c>
+      <c r="J2" s="53" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
@@ -1448,7 +1534,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.15" customHeight="1" s="36">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>💳 TARJETAS Y DEUDA — tu deuda REAL incluye la línea de crédito.</t>
         </is>
@@ -1798,7 +1884,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1813,7 +1899,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.15" customHeight="1" s="36">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>📈 DASHBOARD — del mes activo (ajusta Mes/Año abajo).</t>
         </is>
@@ -2252,7 +2338,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2267,7 +2353,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.15" customHeight="1" s="36">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>🔁 COMPARATIVO — mes activo vs. anterior.</t>
         </is>
@@ -3694,54 +3780,54 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.15" customHeight="1" s="36">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>💰 TRANSACCIONES — base del dinero. El bot escribe aquí tras tu visto bueno.</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="36">
-      <c r="A2" s="52" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B2" s="52" t="inlineStr">
+      <c r="B2" s="53" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C2" s="52" t="inlineStr">
+      <c r="C2" s="53" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="D2" s="52" t="inlineStr">
+      <c r="D2" s="53" t="inlineStr">
         <is>
           <t>Subcategoría</t>
         </is>
       </c>
-      <c r="E2" s="52" t="inlineStr">
+      <c r="E2" s="53" t="inlineStr">
         <is>
           <t>Comercio</t>
         </is>
       </c>
-      <c r="F2" s="52" t="inlineStr">
+      <c r="F2" s="53" t="inlineStr">
         <is>
           <t>Monto</t>
         </is>
       </c>
-      <c r="G2" s="52" t="inlineStr">
+      <c r="G2" s="53" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="H2" s="52" t="inlineStr">
+      <c r="H2" s="53" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="I2" s="52" t="inlineStr">
+      <c r="I2" s="53" t="inlineStr">
         <is>
           <t>ID_Único</t>
         </is>

--- a/docs/Donna_Canonico.xlsx
+++ b/docs/Donna_Canonico.xlsx
@@ -2447,7 +2447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="35" min="1" max="1"/>
@@ -2529,6 +2529,31 @@
       <c r="L2" s="42" t="inlineStr">
         <is>
           <t>Notas</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Primera comida</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Hora desperté</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Agua</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Proteína</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Peso (kg)</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="35" min="1" max="1"/>
@@ -3432,6 +3457,26 @@
       <c r="Q2" s="42" t="inlineStr">
         <is>
           <t>👶 Tiempo hijo</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Score hábitos</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Ventana comida</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Ventana sueño</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Peso</t>
         </is>
       </c>
     </row>

--- a/docs/Donna_Canonico.xlsx
+++ b/docs/Donna_Canonico.xlsx
@@ -2531,27 +2531,27 @@
           <t>Notas</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="35" t="inlineStr">
         <is>
           <t>Primera comida</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="35" t="inlineStr">
         <is>
           <t>Hora desperté</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="35" t="inlineStr">
         <is>
           <t>Agua</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="35" t="inlineStr">
         <is>
           <t>Proteína</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="35" t="inlineStr">
         <is>
           <t>Peso (kg)</t>
         </is>
@@ -3459,22 +3459,22 @@
           <t>👶 Tiempo hijo</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="35" t="inlineStr">
         <is>
           <t>Score hábitos</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" s="35" t="inlineStr">
         <is>
           <t>Ventana comida</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" s="35" t="inlineStr">
         <is>
           <t>Ventana sueño</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" s="35" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
